--- a/public_administration_forms/013_petition_for_improved_veteran_services--public_administration_forms.xlsx
+++ b/public_administration_forms/013_petition_for_improved_veteran_services--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,8 +792,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,12 +821,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'veteran'}</t>
+          <t>veteran</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Veteran'}</t>
+          <t>Veteran</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
